--- a/Proyecto_Python/src/main/resources/matrices/matrix_Caso1_16x16.xlsx
+++ b/Proyecto_Python/src/main/resources/matrices/matrix_Caso1_16x16.xlsx
@@ -564,52 +564,52 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8590276</v>
+        <v>8199491</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2902047</v>
+        <v>2610713</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7148430</v>
+        <v>3715923</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>4535989</v>
+        <v>3351934</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>841946</v>
+        <v>5572571</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>242083</v>
+        <v>6567642</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>999704</v>
+        <v>2445546</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>648717</v>
+        <v>9283343</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>8101548</v>
+        <v>7408003</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1243145</v>
+        <v>4705195</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>5261136</v>
+        <v>6266739</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>7079993</v>
+        <v>4221438</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>9771802</v>
+        <v>5928664</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>9781722</v>
+        <v>4937418</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>3007672</v>
+        <v>5046947</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>4675886</v>
+        <v>9414348</v>
       </c>
     </row>
     <row r="5">
@@ -619,52 +619,52 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5308679</v>
+        <v>6301099</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1595843</v>
+        <v>278306</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1243054</v>
+        <v>3007700</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2753104</v>
+        <v>6351450</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>4320526</v>
+        <v>7172280</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>4600276</v>
+        <v>4587870</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>3521282</v>
+        <v>6760838</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1275558</v>
+        <v>8104270</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1310689</v>
+        <v>1315429</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>8984957</v>
+        <v>7172502</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>1422787</v>
+        <v>1190247</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>2460802</v>
+        <v>7114963</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>5678433</v>
+        <v>5447982</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>3671010</v>
+        <v>7596430</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>9815469</v>
+        <v>8105363</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>3716745</v>
+        <v>2253293</v>
       </c>
     </row>
     <row r="6">
@@ -674,52 +674,52 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>748665</v>
+        <v>6806439</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5590092</v>
+        <v>4245364</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>7664332</v>
+        <v>2874452</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2697044</v>
+        <v>1402247</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2473070</v>
+        <v>814695</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>8312533</v>
+        <v>7576335</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>9836740</v>
+        <v>32460</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>9165628</v>
+        <v>7835792</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>9046309</v>
+        <v>7513135</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4957400</v>
+        <v>6977626</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>3182713</v>
+        <v>8847229</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1624975</v>
+        <v>1570254</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>5224361</v>
+        <v>967170</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>8328813</v>
+        <v>7470654</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>1396433</v>
+        <v>691108</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>2370713</v>
+        <v>1975403</v>
       </c>
     </row>
     <row r="7">
@@ -729,52 +729,52 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2586867</v>
+        <v>9891216</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>690127</v>
+        <v>2412993</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>9295591</v>
+        <v>1922633</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>4802430</v>
+        <v>312723</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2637409</v>
+        <v>5632024</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1445445</v>
+        <v>2378579</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>6033197</v>
+        <v>2421411</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>3843824</v>
+        <v>3849001</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>9949668</v>
+        <v>8550149</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>2843102</v>
+        <v>6657335</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>6867166</v>
+        <v>3042401</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>3711347</v>
+        <v>3143014</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>9521572</v>
+        <v>8467224</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>9039041</v>
+        <v>9182673</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>4388458</v>
+        <v>9366477</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>3463461</v>
+        <v>1327847</v>
       </c>
     </row>
     <row r="8">
@@ -784,52 +784,52 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>9692806</v>
+        <v>1895026</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2627111</v>
+        <v>1513488</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>4305068</v>
+        <v>1572568</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1910237</v>
+        <v>9679126</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4142687</v>
+        <v>7920335</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>3854750</v>
+        <v>5860911</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>4898895</v>
+        <v>402104</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>2372866</v>
+        <v>6023746</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>2525105</v>
+        <v>8746665</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>2060023</v>
+        <v>6212828</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>9510293</v>
+        <v>2152218</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>6485758</v>
+        <v>9452349</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>9920713</v>
+        <v>2724410</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>6725568</v>
+        <v>9891845</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>1630902</v>
+        <v>3229853</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>5827584</v>
+        <v>6135393</v>
       </c>
     </row>
     <row r="9">
@@ -839,52 +839,52 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>8248055</v>
+        <v>7000258</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2254730</v>
+        <v>9159141</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>8533190</v>
+        <v>7638022</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>8778576</v>
+        <v>9970391</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1446976</v>
+        <v>3297443</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1345892</v>
+        <v>2211307</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1507466</v>
+        <v>8967673</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>4347163</v>
+        <v>9037330</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>3161126</v>
+        <v>7272566</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>4333773</v>
+        <v>7632972</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>635808</v>
+        <v>1253321</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>8844626</v>
+        <v>6528623</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>5299254</v>
+        <v>5894028</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>5566333</v>
+        <v>3148353</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>8707659</v>
+        <v>4526527</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>8821770</v>
+        <v>8927155</v>
       </c>
     </row>
     <row r="10">
@@ -894,52 +894,52 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8859878</v>
+        <v>8066329</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>9474736</v>
+        <v>4885060</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1434977</v>
+        <v>3945693</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1059613</v>
+        <v>1267670</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>305308</v>
+        <v>4572746</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1857659</v>
+        <v>8176013</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>6207658</v>
+        <v>4800019</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>4836063</v>
+        <v>7074187</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>8210032</v>
+        <v>7298005</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>3109262</v>
+        <v>7278234</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>9197205</v>
+        <v>2332013</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>7076533</v>
+        <v>6382878</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>5200829</v>
+        <v>8725434</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>1432710</v>
+        <v>5258727</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>13673</v>
+        <v>9991542</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>6463568</v>
+        <v>1581810</v>
       </c>
     </row>
     <row r="11">
@@ -949,52 +949,52 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5329424</v>
+        <v>581783</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>9747750</v>
+        <v>3501276</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7348148</v>
+        <v>3834025</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>4833875</v>
+        <v>8224377</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>9528213</v>
+        <v>6681300</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5713014</v>
+        <v>4166483</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>6639150</v>
+        <v>6228087</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1485035</v>
+        <v>6546401</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>6050941</v>
+        <v>7893170</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>8696695</v>
+        <v>6420942</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>1917283</v>
+        <v>96933</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>7091254</v>
+        <v>288162</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>3286644</v>
+        <v>8053764</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>8707063</v>
+        <v>4464722</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>1467373</v>
+        <v>3932525</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>657671</v>
+        <v>4308122</v>
       </c>
     </row>
     <row r="12">
@@ -1004,52 +1004,52 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5642749</v>
+        <v>1785245</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>4469325</v>
+        <v>2159678</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>6063845</v>
+        <v>8022530</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>9129776</v>
+        <v>5676305</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>6128120</v>
+        <v>3240178</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2680452</v>
+        <v>862917</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>7171241</v>
+        <v>2827211</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>6104280</v>
+        <v>2586232</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>6937905</v>
+        <v>8637227</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>4691943</v>
+        <v>6758678</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>5297961</v>
+        <v>8131027</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>9578644</v>
+        <v>7855185</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>7097038</v>
+        <v>3197311</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>7184229</v>
+        <v>3159594</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>3691475</v>
+        <v>1531505</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>8456072</v>
+        <v>7252394</v>
       </c>
     </row>
     <row r="13">
@@ -1059,52 +1059,52 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>5921296</v>
+        <v>2831382</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2182948</v>
+        <v>3742977</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>9661159</v>
+        <v>7125326</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>6795509</v>
+        <v>657343</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>454255</v>
+        <v>5920537</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>3231102</v>
+        <v>7645216</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>9835488</v>
+        <v>2861734</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>2428948</v>
+        <v>8184881</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>6771617</v>
+        <v>3844834</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>9622331</v>
+        <v>9367756</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>5980043</v>
+        <v>8210231</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>3920810</v>
+        <v>7939385</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>1291375</v>
+        <v>4288316</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>7911485</v>
+        <v>4594151</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>45908</v>
+        <v>6826377</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>4046473</v>
+        <v>5932494</v>
       </c>
     </row>
     <row r="14">
@@ -1114,52 +1114,52 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>6661231</v>
+        <v>5604302</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>7415176</v>
+        <v>8294453</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>417063</v>
+        <v>6267609</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7515413</v>
+        <v>53081</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>546018</v>
+        <v>920289</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>8561552</v>
+        <v>4727660</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>5513555</v>
+        <v>9812475</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>580612</v>
+        <v>4288279</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>5532089</v>
+        <v>3452617</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>1274463</v>
+        <v>8640851</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>4774957</v>
+        <v>3601940</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>3509330</v>
+        <v>4428174</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>5307193</v>
+        <v>5761455</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>7496889</v>
+        <v>8431149</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>3263623</v>
+        <v>4807955</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>8169785</v>
+        <v>9500235</v>
       </c>
     </row>
     <row r="15">
@@ -1169,52 +1169,52 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>6099490</v>
+        <v>7391120</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1316189</v>
+        <v>5193163</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6655112</v>
+        <v>8106493</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>9850393</v>
+        <v>8785900</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>2703638</v>
+        <v>8956489</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>545076</v>
+        <v>7230469</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>3275491</v>
+        <v>3167166</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>8100225</v>
+        <v>47399</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>598088</v>
+        <v>9067907</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>4744364</v>
+        <v>6830138</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>207220</v>
+        <v>2894405</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>6736188</v>
+        <v>6500572</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>6018478</v>
+        <v>7985274</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>6377345</v>
+        <v>7846232</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>7548597</v>
+        <v>1686422</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>208130</v>
+        <v>3575609</v>
       </c>
     </row>
     <row r="16">
@@ -1224,52 +1224,52 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>5203076</v>
+        <v>7573541</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>3304505</v>
+        <v>8672759</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>7025010</v>
+        <v>5421258</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>4390570</v>
+        <v>2306002</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>675769</v>
+        <v>1879127</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>4845737</v>
+        <v>768954</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>9498111</v>
+        <v>5019440</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>9536895</v>
+        <v>3171183</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>6681193</v>
+        <v>9734005</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>5522389</v>
+        <v>1831617</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>683937</v>
+        <v>4414855</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>6668845</v>
+        <v>5450336</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>2574527</v>
+        <v>1179182</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1046376</v>
+        <v>6096469</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>3843074</v>
+        <v>3217469</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>7470227</v>
+        <v>9220085</v>
       </c>
     </row>
     <row r="17">
@@ -1279,52 +1279,52 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3783480</v>
+        <v>3328820</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>6115064</v>
+        <v>632911</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4073496</v>
+        <v>6269478</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4037449</v>
+        <v>1361449</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>7254522</v>
+        <v>2212500</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>5045785</v>
+        <v>934809</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>5216319</v>
+        <v>9463197</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>4179613</v>
+        <v>1720581</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>7413558</v>
+        <v>3043941</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>4060506</v>
+        <v>7726173</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>8792408</v>
+        <v>7912757</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>4613686</v>
+        <v>6164057</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>9503806</v>
+        <v>4685368</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>6932798</v>
+        <v>1088076</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>2541346</v>
+        <v>5525042</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>2719671</v>
+        <v>6906104</v>
       </c>
     </row>
     <row r="18">
@@ -1334,52 +1334,52 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>3785290</v>
+        <v>2957458</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>7968373</v>
+        <v>7772294</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>8599155</v>
+        <v>9403679</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>5705642</v>
+        <v>6755910</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>5484981</v>
+        <v>8161840</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>2555547</v>
+        <v>4618138</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>5601929</v>
+        <v>4257821</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>5004736</v>
+        <v>4143429</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4023632</v>
+        <v>9706121</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>1919905</v>
+        <v>7599166</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>5425223</v>
+        <v>1630508</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>828645</v>
+        <v>2406509</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>9933601</v>
+        <v>9161993</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>373048</v>
+        <v>2569863</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>1136241</v>
+        <v>8899807</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>8637627</v>
+        <v>2775315</v>
       </c>
     </row>
     <row r="19">
@@ -1389,52 +1389,52 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1663026</v>
+        <v>5287528</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2996920</v>
+        <v>4365446</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6504905</v>
+        <v>1406271</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>5422226</v>
+        <v>9195436</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>8701364</v>
+        <v>1322816</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>7603571</v>
+        <v>7913303</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>8913982</v>
+        <v>3298336</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>937679</v>
+        <v>9004872</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>2869551</v>
+        <v>362460</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>2292593</v>
+        <v>6171267</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>1029239</v>
+        <v>8502035</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>7996493</v>
+        <v>624675</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>6300063</v>
+        <v>3998075</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>5522594</v>
+        <v>3261838</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>8533433</v>
+        <v>590484</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>1599976</v>
+        <v>9444107</v>
       </c>
     </row>
   </sheetData>
@@ -1569,52 +1569,52 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1543637</v>
+        <v>4199662</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>617292</v>
+        <v>9016727</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2508788</v>
+        <v>8291961</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>8082697</v>
+        <v>4543454</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>3073329</v>
+        <v>4655852</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>524797</v>
+        <v>8754401</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2278528</v>
+        <v>5575769</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>6035671</v>
+        <v>9995864</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>5858483</v>
+        <v>5135926</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>537921</v>
+        <v>5783334</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>5711771</v>
+        <v>6385595</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>684815</v>
+        <v>2382132</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>4519764</v>
+        <v>9325827</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>8743303</v>
+        <v>2506109</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>3021921</v>
+        <v>4141467</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>9525526</v>
+        <v>6607332</v>
       </c>
     </row>
     <row r="5">
@@ -1624,52 +1624,52 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4253036</v>
+        <v>9358125</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3338413</v>
+        <v>635979</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>561223</v>
+        <v>8402423</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>8033233</v>
+        <v>6888578</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>8871133</v>
+        <v>3640027</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>7347007</v>
+        <v>8327039</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2525596</v>
+        <v>7590171</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>7290179</v>
+        <v>2700994</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>4763652</v>
+        <v>6732042</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>3672675</v>
+        <v>216575</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>2385177</v>
+        <v>2770168</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>596077</v>
+        <v>510529</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>4813335</v>
+        <v>3514861</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>5528571</v>
+        <v>4331117</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>4609408</v>
+        <v>3194646</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>2731860</v>
+        <v>672858</v>
       </c>
     </row>
     <row r="6">
@@ -1679,52 +1679,52 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2530816</v>
+        <v>1437509</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3937685</v>
+        <v>5153678</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2949879</v>
+        <v>7935367</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>6134366</v>
+        <v>8776902</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>9473251</v>
+        <v>3036926</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>2107932</v>
+        <v>5932771</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>5243207</v>
+        <v>5441724</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>7340956</v>
+        <v>3727089</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1669560</v>
+        <v>2202178</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1611585</v>
+        <v>2406037</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>1394689</v>
+        <v>5189003</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>828218</v>
+        <v>4387414</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>5213168</v>
+        <v>3540306</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>7838792</v>
+        <v>7260962</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>6860089</v>
+        <v>8432142</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>6834748</v>
+        <v>2458260</v>
       </c>
     </row>
     <row r="7">
@@ -1734,52 +1734,52 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1573384</v>
+        <v>2049195</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2555287</v>
+        <v>6002420</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>8332320</v>
+        <v>797273</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3696075</v>
+        <v>6089672</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>7494042</v>
+        <v>3740237</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1839557</v>
+        <v>4406085</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>5767741</v>
+        <v>5645909</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>9444263</v>
+        <v>7696023</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>5426274</v>
+        <v>5507050</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>7149436</v>
+        <v>2534850</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>4377673</v>
+        <v>6629936</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>5453750</v>
+        <v>1021221</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>7122004</v>
+        <v>8626754</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>8120273</v>
+        <v>3554499</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>5471188</v>
+        <v>7787932</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>2069477</v>
+        <v>7497842</v>
       </c>
     </row>
     <row r="8">
@@ -1789,52 +1789,52 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1799880</v>
+        <v>4958029</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>6869933</v>
+        <v>8735180</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>607404</v>
+        <v>4514592</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>5638106</v>
+        <v>8263855</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>3508605</v>
+        <v>5956864</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>9489172</v>
+        <v>229729</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7151609</v>
+        <v>1913397</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>9225548</v>
+        <v>5822889</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>8411160</v>
+        <v>4157667</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>2156501</v>
+        <v>4047204</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>388285</v>
+        <v>9823524</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>6531559</v>
+        <v>1261760</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>5906670</v>
+        <v>357215</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>6078587</v>
+        <v>7725753</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>7759383</v>
+        <v>3977534</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>4200426</v>
+        <v>4401731</v>
       </c>
     </row>
     <row r="9">
@@ -1844,52 +1844,52 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>896259</v>
+        <v>5279469</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>4023450</v>
+        <v>3951856</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>8197699</v>
+        <v>4175941</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7776515</v>
+        <v>5784989</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>5368961</v>
+        <v>1214373</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>2591305</v>
+        <v>4162679</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>3639765</v>
+        <v>2179042</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>5151908</v>
+        <v>7178291</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>8817226</v>
+        <v>2253383</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>5732766</v>
+        <v>7275398</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>4306156</v>
+        <v>6049403</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>382603</v>
+        <v>509849</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>9520353</v>
+        <v>393645</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>5090904</v>
+        <v>5090347</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>5092920</v>
+        <v>4849618</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>5041099</v>
+        <v>6158030</v>
       </c>
     </row>
     <row r="10">
@@ -1899,52 +1899,52 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>7291510</v>
+        <v>2576266</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>5016048</v>
+        <v>2085239</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>5999704</v>
+        <v>6481652</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5396484</v>
+        <v>9647181</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>6795737</v>
+        <v>7876287</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>9130634</v>
+        <v>5605374</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>2856545</v>
+        <v>8068114</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>9566203</v>
+        <v>1342408</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>5749520</v>
+        <v>6552380</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>7131316</v>
+        <v>3838070</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>3621140</v>
+        <v>1629441</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>7097130</v>
+        <v>1856981</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>543089</v>
+        <v>6721449</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>2456367</v>
+        <v>5033894</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>7101698</v>
+        <v>4305560</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>5768809</v>
+        <v>2799325</v>
       </c>
     </row>
     <row r="11">
@@ -1954,52 +1954,52 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1315107</v>
+        <v>8476643</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>6554055</v>
+        <v>3850864</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7231921</v>
+        <v>6574735</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>119463</v>
+        <v>5265246</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>605096</v>
+        <v>9985295</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>4252424</v>
+        <v>895274</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>5756043</v>
+        <v>1344734</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4042265</v>
+        <v>6060721</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>9040018</v>
+        <v>1918061</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>8583113</v>
+        <v>8027694</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>8651986</v>
+        <v>9515797</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>5535999</v>
+        <v>2676276</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>3460888</v>
+        <v>8513686</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>4690351</v>
+        <v>4218907</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>1258204</v>
+        <v>6626652</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>1807444</v>
+        <v>9297393</v>
       </c>
     </row>
     <row r="12">
@@ -2009,52 +2009,52 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>9639477</v>
+        <v>8638567</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>6918360</v>
+        <v>8192890</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>6695250</v>
+        <v>9135629</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7620463</v>
+        <v>4703193</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4639853</v>
+        <v>3160155</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1105495</v>
+        <v>1791837</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>165560</v>
+        <v>1865092</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2196504</v>
+        <v>1446999</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>4424646</v>
+        <v>4700115</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>9163164</v>
+        <v>4280157</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>8868448</v>
+        <v>367268</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>1856750</v>
+        <v>2800679</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>5232167</v>
+        <v>5936521</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>4622651</v>
+        <v>9825055</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>7400136</v>
+        <v>2533556</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>6271695</v>
+        <v>7827414</v>
       </c>
     </row>
     <row r="13">
@@ -2064,52 +2064,52 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>5352667</v>
+        <v>6058548</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>9538360</v>
+        <v>745167</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>7918647</v>
+        <v>617632</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7674762</v>
+        <v>7382691</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>9531870</v>
+        <v>1617282</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>3964604</v>
+        <v>398333</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>3641199</v>
+        <v>3458076</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>5993276</v>
+        <v>6067412</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>3651814</v>
+        <v>8380492</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>7307020</v>
+        <v>284119</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>6449146</v>
+        <v>6993811</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>8678697</v>
+        <v>5714973</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>9777677</v>
+        <v>1317776</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>9872599</v>
+        <v>3739946</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>1265792</v>
+        <v>797533</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>3410125</v>
+        <v>6389303</v>
       </c>
     </row>
     <row r="14">
@@ -2119,52 +2119,52 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>8634699</v>
+        <v>4989094</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>854541</v>
+        <v>4272418</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>9996733</v>
+        <v>268782</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>4872128</v>
+        <v>294568</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6946277</v>
+        <v>6510677</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1505052</v>
+        <v>1849638</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1592653</v>
+        <v>7305861</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>8945953</v>
+        <v>9745687</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1154741</v>
+        <v>122022</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>3855948</v>
+        <v>71002</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>5522546</v>
+        <v>1710210</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>8824056</v>
+        <v>3908936</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>2730536</v>
+        <v>6564997</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>325983</v>
+        <v>1878753</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>6978001</v>
+        <v>959051</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>5385154</v>
+        <v>2959363</v>
       </c>
     </row>
     <row r="15">
@@ -2174,52 +2174,52 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9771854</v>
+        <v>2120379</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>8187541</v>
+        <v>2213144</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>2746822</v>
+        <v>5670271</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7104574</v>
+        <v>6605698</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>6264811</v>
+        <v>7485902</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>76300</v>
+        <v>7941032</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>7544919</v>
+        <v>164080</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>5608419</v>
+        <v>183639</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>3070787</v>
+        <v>6120892</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>1088202</v>
+        <v>628467</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>9895264</v>
+        <v>6740548</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>6874724</v>
+        <v>6391547</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>4031629</v>
+        <v>6599103</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>5318533</v>
+        <v>4576187</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>6219087</v>
+        <v>8086583</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>3413856</v>
+        <v>4833515</v>
       </c>
     </row>
     <row r="16">
@@ -2229,52 +2229,52 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3848334</v>
+        <v>5803758</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>7851523</v>
+        <v>1774327</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>4505256</v>
+        <v>2054661</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>6241485</v>
+        <v>5780282</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>585846</v>
+        <v>8140814</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>8710985</v>
+        <v>4844291</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>8036130</v>
+        <v>8634642</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>9865566</v>
+        <v>4447354</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2104878</v>
+        <v>7390030</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>723154</v>
+        <v>8932507</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>9815163</v>
+        <v>9124291</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>8631483</v>
+        <v>4498492</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>4462374</v>
+        <v>7028290</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>5762928</v>
+        <v>8237353</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>8211700</v>
+        <v>3297504</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>6383482</v>
+        <v>6973935</v>
       </c>
     </row>
     <row r="17">
@@ -2284,52 +2284,52 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>6409140</v>
+        <v>9396126</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>7925042</v>
+        <v>7604427</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6973029</v>
+        <v>9450333</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4636831</v>
+        <v>5771267</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1861175</v>
+        <v>1864484</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>9557308</v>
+        <v>468846</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>8788192</v>
+        <v>9750646</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>8827753</v>
+        <v>8544294</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>171309</v>
+        <v>6376055</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>7476847</v>
+        <v>7425801</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>4866387</v>
+        <v>3374796</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>5478842</v>
+        <v>30597</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>1729375</v>
+        <v>9922048</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1877964</v>
+        <v>604404</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>3590624</v>
+        <v>2997599</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>8480742</v>
+        <v>2836678</v>
       </c>
     </row>
     <row r="18">
@@ -2339,52 +2339,52 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>8152208</v>
+        <v>4074375</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>3137903</v>
+        <v>9788766</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4764255</v>
+        <v>3193630</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>5460082</v>
+        <v>7559889</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1364504</v>
+        <v>7795867</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1321121</v>
+        <v>5225729</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>9325787</v>
+        <v>7199595</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2633885</v>
+        <v>7804493</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>6890870</v>
+        <v>5195932</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>4726734</v>
+        <v>179329</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>7599533</v>
+        <v>6063037</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>8632861</v>
+        <v>6088547</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>227241</v>
+        <v>8312006</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>4341713</v>
+        <v>9220432</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>5043117</v>
+        <v>8989707</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>4947776</v>
+        <v>9923462</v>
       </c>
     </row>
     <row r="19">
@@ -2394,52 +2394,52 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>7613310</v>
+        <v>7611827</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>9861386</v>
+        <v>1378185</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3782160</v>
+        <v>1725739</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>8253254</v>
+        <v>8499186</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>9963367</v>
+        <v>1492377</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>994200</v>
+        <v>3558075</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>3766937</v>
+        <v>4500421</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1275332</v>
+        <v>3000741</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>4883429</v>
+        <v>5618974</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>2727455</v>
+        <v>5459010</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>6730645</v>
+        <v>5767563</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>3480232</v>
+        <v>2496736</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>8062578</v>
+        <v>8338076</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>6187196</v>
+        <v>6574460</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>9425397</v>
+        <v>5306011</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>3365861</v>
+        <v>1795256</v>
       </c>
     </row>
   </sheetData>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-04-25 10:57:54</t>
+          <t>2026-04-25 11:29:47</t>
         </is>
       </c>
     </row>

--- a/Proyecto_Python/src/main/resources/matrices/matrix_Caso1_16x16.xlsx
+++ b/Proyecto_Python/src/main/resources/matrices/matrix_Caso1_16x16.xlsx
@@ -564,52 +564,52 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8199491</v>
+        <v>187754</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2610713</v>
+        <v>2586262</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3715923</v>
+        <v>6989019</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3351934</v>
+        <v>5513000</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>5572571</v>
+        <v>9249497</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>6567642</v>
+        <v>7751456</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2445546</v>
+        <v>7299047</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>9283343</v>
+        <v>1079427</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>7408003</v>
+        <v>9886625</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>4705195</v>
+        <v>6254144</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>6266739</v>
+        <v>1132945</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>4221438</v>
+        <v>4780489</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>5928664</v>
+        <v>3073507</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>4937418</v>
+        <v>8190965</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>5046947</v>
+        <v>4350842</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>9414348</v>
+        <v>2564243</v>
       </c>
     </row>
     <row r="5">
@@ -619,52 +619,52 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6301099</v>
+        <v>60166</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>278306</v>
+        <v>4684894</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3007700</v>
+        <v>8291369</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>6351450</v>
+        <v>1117094</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>7172280</v>
+        <v>4775398</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>4587870</v>
+        <v>1573416</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>6760838</v>
+        <v>7476603</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>8104270</v>
+        <v>2686495</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1315429</v>
+        <v>8750954</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>7172502</v>
+        <v>9244292</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>1190247</v>
+        <v>8364804</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>7114963</v>
+        <v>7794862</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>5447982</v>
+        <v>2585746</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>7596430</v>
+        <v>6151742</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>8105363</v>
+        <v>2938236</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>2253293</v>
+        <v>1204538</v>
       </c>
     </row>
     <row r="6">
@@ -674,52 +674,52 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>6806439</v>
+        <v>8227756</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4245364</v>
+        <v>2678847</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2874452</v>
+        <v>2986882</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1402247</v>
+        <v>2350996</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>814695</v>
+        <v>6698724</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>7576335</v>
+        <v>2229420</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>32460</v>
+        <v>9062277</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>7835792</v>
+        <v>774423</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>7513135</v>
+        <v>1047491</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>6977626</v>
+        <v>943080</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>8847229</v>
+        <v>1959050</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1570254</v>
+        <v>8269544</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>967170</v>
+        <v>7944883</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>7470654</v>
+        <v>7379899</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>691108</v>
+        <v>8582236</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1975403</v>
+        <v>9190677</v>
       </c>
     </row>
     <row r="7">
@@ -729,52 +729,52 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>9891216</v>
+        <v>7825849</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2412993</v>
+        <v>5386624</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1922633</v>
+        <v>1305019</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>312723</v>
+        <v>2584080</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5632024</v>
+        <v>1532471</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2378579</v>
+        <v>4627029</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2421411</v>
+        <v>896664</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>3849001</v>
+        <v>4617813</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>8550149</v>
+        <v>3108487</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>6657335</v>
+        <v>3422039</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>3042401</v>
+        <v>7936924</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>3143014</v>
+        <v>3009732</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>8467224</v>
+        <v>7989522</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>9182673</v>
+        <v>683861</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>9366477</v>
+        <v>543968</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1327847</v>
+        <v>1334814</v>
       </c>
     </row>
     <row r="8">
@@ -784,52 +784,52 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1895026</v>
+        <v>2647843</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1513488</v>
+        <v>3568185</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1572568</v>
+        <v>6273784</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>9679126</v>
+        <v>8199802</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>7920335</v>
+        <v>4565900</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>5860911</v>
+        <v>3020840</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>402104</v>
+        <v>6629832</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>6023746</v>
+        <v>7256516</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>8746665</v>
+        <v>9755928</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>6212828</v>
+        <v>1306413</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>2152218</v>
+        <v>1852288</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>9452349</v>
+        <v>9249263</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>2724410</v>
+        <v>3979083</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>9891845</v>
+        <v>6089415</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>3229853</v>
+        <v>2878829</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>6135393</v>
+        <v>4106073</v>
       </c>
     </row>
     <row r="9">
@@ -839,52 +839,52 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7000258</v>
+        <v>7107044</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>9159141</v>
+        <v>899169</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>7638022</v>
+        <v>1174317</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>9970391</v>
+        <v>6990330</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>3297443</v>
+        <v>1796914</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>2211307</v>
+        <v>9654209</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>8967673</v>
+        <v>8049976</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>9037330</v>
+        <v>2498035</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>7272566</v>
+        <v>5120630</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>7632972</v>
+        <v>6622123</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>1253321</v>
+        <v>1829155</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>6528623</v>
+        <v>6559546</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>5894028</v>
+        <v>2179487</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>3148353</v>
+        <v>8307163</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>4526527</v>
+        <v>3506773</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>8927155</v>
+        <v>2261479</v>
       </c>
     </row>
     <row r="10">
@@ -894,52 +894,52 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8066329</v>
+        <v>4876946</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4885060</v>
+        <v>1066464</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3945693</v>
+        <v>5560537</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1267670</v>
+        <v>9664546</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4572746</v>
+        <v>6246404</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8176013</v>
+        <v>6707134</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>4800019</v>
+        <v>2087576</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>7074187</v>
+        <v>9982160</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>7298005</v>
+        <v>1554789</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>7278234</v>
+        <v>588057</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>2332013</v>
+        <v>9051645</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>6382878</v>
+        <v>6419567</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>8725434</v>
+        <v>4539073</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>5258727</v>
+        <v>9370722</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>9991542</v>
+        <v>8946041</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>1581810</v>
+        <v>8336899</v>
       </c>
     </row>
     <row r="11">
@@ -949,52 +949,52 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>581783</v>
+        <v>3339753</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>3501276</v>
+        <v>3031050</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3834025</v>
+        <v>628891</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>8224377</v>
+        <v>4056194</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>6681300</v>
+        <v>4318759</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>4166483</v>
+        <v>8297214</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>6228087</v>
+        <v>9725609</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>6546401</v>
+        <v>8428257</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>7893170</v>
+        <v>2208056</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>6420942</v>
+        <v>7790108</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>96933</v>
+        <v>5598886</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>288162</v>
+        <v>89657</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>8053764</v>
+        <v>8704381</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>4464722</v>
+        <v>442159</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>3932525</v>
+        <v>7876663</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>4308122</v>
+        <v>6753344</v>
       </c>
     </row>
     <row r="12">
@@ -1004,52 +1004,52 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1785245</v>
+        <v>6127717</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2159678</v>
+        <v>3264273</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>8022530</v>
+        <v>2264902</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5676305</v>
+        <v>4543937</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>3240178</v>
+        <v>4892414</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>862917</v>
+        <v>716742</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>2827211</v>
+        <v>2288317</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2586232</v>
+        <v>8473867</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>8637227</v>
+        <v>3333504</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>6758678</v>
+        <v>3928030</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>8131027</v>
+        <v>2415555</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>7855185</v>
+        <v>4808120</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>3197311</v>
+        <v>5408801</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>3159594</v>
+        <v>903678</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>1531505</v>
+        <v>2504633</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>7252394</v>
+        <v>6066155</v>
       </c>
     </row>
     <row r="13">
@@ -1059,52 +1059,52 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2831382</v>
+        <v>7148376</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3742977</v>
+        <v>4218125</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>7125326</v>
+        <v>7383219</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>657343</v>
+        <v>8020905</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>5920537</v>
+        <v>5105332</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>7645216</v>
+        <v>1926054</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>2861734</v>
+        <v>3908265</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>8184881</v>
+        <v>3663736</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>3844834</v>
+        <v>7505943</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>9367756</v>
+        <v>8256950</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>8210231</v>
+        <v>4615337</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>7939385</v>
+        <v>1043522</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>4288316</v>
+        <v>2019154</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>4594151</v>
+        <v>5171077</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>6826377</v>
+        <v>9923688</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>5932494</v>
+        <v>2208488</v>
       </c>
     </row>
     <row r="14">
@@ -1114,52 +1114,52 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5604302</v>
+        <v>1622878</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>8294453</v>
+        <v>8850907</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>6267609</v>
+        <v>4477327</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>53081</v>
+        <v>1622855</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>920289</v>
+        <v>587027</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>4727660</v>
+        <v>6443032</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>9812475</v>
+        <v>706459</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>4288279</v>
+        <v>8045853</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>3452617</v>
+        <v>7967379</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8640851</v>
+        <v>6487923</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>3601940</v>
+        <v>8633808</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>4428174</v>
+        <v>4551981</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>5761455</v>
+        <v>5010986</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>8431149</v>
+        <v>1193079</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>4807955</v>
+        <v>2868916</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>9500235</v>
+        <v>5415366</v>
       </c>
     </row>
     <row r="15">
@@ -1169,52 +1169,52 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>7391120</v>
+        <v>5981947</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>5193163</v>
+        <v>7976476</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>8106493</v>
+        <v>7393204</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>8785900</v>
+        <v>4705121</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>8956489</v>
+        <v>9454749</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>7230469</v>
+        <v>1245460</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>3167166</v>
+        <v>9707786</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>47399</v>
+        <v>841833</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>9067907</v>
+        <v>1798930</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>6830138</v>
+        <v>5416975</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>2894405</v>
+        <v>2926334</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>6500572</v>
+        <v>1901185</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>7985274</v>
+        <v>5746991</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>7846232</v>
+        <v>1150259</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>1686422</v>
+        <v>8623290</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>3575609</v>
+        <v>2936834</v>
       </c>
     </row>
     <row r="16">
@@ -1224,52 +1224,52 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>7573541</v>
+        <v>2450313</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8672759</v>
+        <v>869578</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5421258</v>
+        <v>5450391</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2306002</v>
+        <v>8438553</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1879127</v>
+        <v>5286359</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>768954</v>
+        <v>5001547</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>5019440</v>
+        <v>649993</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>3171183</v>
+        <v>9162961</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>9734005</v>
+        <v>3484364</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1831617</v>
+        <v>4491647</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>4414855</v>
+        <v>8936275</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>5450336</v>
+        <v>6076171</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1179182</v>
+        <v>5045785</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>6096469</v>
+        <v>7932763</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>3217469</v>
+        <v>8602205</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>9220085</v>
+        <v>9072033</v>
       </c>
     </row>
     <row r="17">
@@ -1279,52 +1279,52 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3328820</v>
+        <v>5525699</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>632911</v>
+        <v>7626366</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>6269478</v>
+        <v>4806550</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1361449</v>
+        <v>3741848</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>2212500</v>
+        <v>8846218</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>934809</v>
+        <v>312151</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>9463197</v>
+        <v>4180785</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1720581</v>
+        <v>9451783</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3043941</v>
+        <v>8282970</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>7726173</v>
+        <v>8606314</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>7912757</v>
+        <v>7345026</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>6164057</v>
+        <v>5707050</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>4685368</v>
+        <v>1203041</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1088076</v>
+        <v>6718156</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>5525042</v>
+        <v>9775426</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>6906104</v>
+        <v>5249038</v>
       </c>
     </row>
     <row r="18">
@@ -1334,52 +1334,52 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2957458</v>
+        <v>7533704</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>7772294</v>
+        <v>9537097</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>9403679</v>
+        <v>4052469</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>6755910</v>
+        <v>2511341</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>8161840</v>
+        <v>1321875</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>4618138</v>
+        <v>697026</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>4257821</v>
+        <v>2366229</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>4143429</v>
+        <v>250082</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>9706121</v>
+        <v>90464</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>7599166</v>
+        <v>4916979</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>1630508</v>
+        <v>5397485</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>2406509</v>
+        <v>7838429</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>9161993</v>
+        <v>7200369</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>2569863</v>
+        <v>9660181</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>8899807</v>
+        <v>8866555</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>2775315</v>
+        <v>2544791</v>
       </c>
     </row>
     <row r="19">
@@ -1389,52 +1389,52 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5287528</v>
+        <v>6949281</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4365446</v>
+        <v>824531</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1406271</v>
+        <v>494457</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>9195436</v>
+        <v>2029726</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1322816</v>
+        <v>4869774</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>7913303</v>
+        <v>199698</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>3298336</v>
+        <v>9450352</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>9004872</v>
+        <v>7918598</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>362460</v>
+        <v>6230554</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>6171267</v>
+        <v>8599321</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>8502035</v>
+        <v>3122201</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>624675</v>
+        <v>7077893</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>3998075</v>
+        <v>2416491</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>3261838</v>
+        <v>4696918</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>590484</v>
+        <v>8858768</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>9444107</v>
+        <v>5065782</v>
       </c>
     </row>
   </sheetData>
@@ -1569,52 +1569,52 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4199662</v>
+        <v>2766826</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>9016727</v>
+        <v>2860842</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>8291961</v>
+        <v>3278562</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>4543454</v>
+        <v>6412583</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>4655852</v>
+        <v>6777233</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>8754401</v>
+        <v>5750087</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5575769</v>
+        <v>7893141</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>9995864</v>
+        <v>9726427</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>5135926</v>
+        <v>3759464</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>5783334</v>
+        <v>9356494</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>6385595</v>
+        <v>6373029</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>2382132</v>
+        <v>3717786</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>9325827</v>
+        <v>2649253</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>2506109</v>
+        <v>5568146</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>4141467</v>
+        <v>464677</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>6607332</v>
+        <v>4065983</v>
       </c>
     </row>
     <row r="5">
@@ -1624,52 +1624,52 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>9358125</v>
+        <v>7136761</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>635979</v>
+        <v>7065691</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>8402423</v>
+        <v>7850647</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>6888578</v>
+        <v>7003045</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3640027</v>
+        <v>8988509</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>8327039</v>
+        <v>6454079</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>7590171</v>
+        <v>4117112</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>2700994</v>
+        <v>2112415</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>6732042</v>
+        <v>5207953</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>216575</v>
+        <v>2314730</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>2770168</v>
+        <v>7457526</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>510529</v>
+        <v>5675473</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>3514861</v>
+        <v>9356558</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>4331117</v>
+        <v>8321105</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>3194646</v>
+        <v>7446837</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>672858</v>
+        <v>7320238</v>
       </c>
     </row>
     <row r="6">
@@ -1679,52 +1679,52 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1437509</v>
+        <v>4511172</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5153678</v>
+        <v>6681707</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>7935367</v>
+        <v>9820584</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>8776902</v>
+        <v>4221232</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3036926</v>
+        <v>9710113</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>5932771</v>
+        <v>5985192</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>5441724</v>
+        <v>4668488</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>3727089</v>
+        <v>3966488</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2202178</v>
+        <v>586813</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>2406037</v>
+        <v>6148173</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>5189003</v>
+        <v>1512012</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>4387414</v>
+        <v>8856644</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>3540306</v>
+        <v>3283235</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>7260962</v>
+        <v>4581923</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>8432142</v>
+        <v>5720997</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>2458260</v>
+        <v>9012281</v>
       </c>
     </row>
     <row r="7">
@@ -1734,52 +1734,52 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2049195</v>
+        <v>5180174</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6002420</v>
+        <v>8009336</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>797273</v>
+        <v>2338812</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>6089672</v>
+        <v>9816659</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3740237</v>
+        <v>3247428</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>4406085</v>
+        <v>363967</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>5645909</v>
+        <v>1379274</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>7696023</v>
+        <v>594892</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>5507050</v>
+        <v>6797505</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>2534850</v>
+        <v>2680733</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>6629936</v>
+        <v>3226177</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1021221</v>
+        <v>468337</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>8626754</v>
+        <v>7349995</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>3554499</v>
+        <v>8704800</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>7787932</v>
+        <v>2981075</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>7497842</v>
+        <v>344430</v>
       </c>
     </row>
     <row r="8">
@@ -1789,52 +1789,52 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>4958029</v>
+        <v>6066539</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>8735180</v>
+        <v>8455067</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>4514592</v>
+        <v>8270030</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>8263855</v>
+        <v>1390879</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>5956864</v>
+        <v>6472628</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>229729</v>
+        <v>434088</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1913397</v>
+        <v>5500842</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>5822889</v>
+        <v>5247009</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>4157667</v>
+        <v>6149996</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>4047204</v>
+        <v>2104194</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>9823524</v>
+        <v>2062240</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1261760</v>
+        <v>3150100</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>357215</v>
+        <v>2731649</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>7725753</v>
+        <v>5202735</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>3977534</v>
+        <v>7955120</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>4401731</v>
+        <v>4996094</v>
       </c>
     </row>
     <row r="9">
@@ -1844,52 +1844,52 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>5279469</v>
+        <v>5352759</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3951856</v>
+        <v>1818997</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4175941</v>
+        <v>9532926</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>5784989</v>
+        <v>2055731</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1214373</v>
+        <v>1526024</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>4162679</v>
+        <v>4926318</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>2179042</v>
+        <v>5019335</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>7178291</v>
+        <v>5641794</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>2253383</v>
+        <v>3911756</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>7275398</v>
+        <v>8006062</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>6049403</v>
+        <v>7932165</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>509849</v>
+        <v>2305967</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>393645</v>
+        <v>8832821</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>5090347</v>
+        <v>6009257</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>4849618</v>
+        <v>1470763</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>6158030</v>
+        <v>1591707</v>
       </c>
     </row>
     <row r="10">
@@ -1899,52 +1899,52 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2576266</v>
+        <v>7539459</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2085239</v>
+        <v>5445224</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>6481652</v>
+        <v>4407543</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>9647181</v>
+        <v>1961160</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>7876287</v>
+        <v>1343750</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>5605374</v>
+        <v>1269298</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>8068114</v>
+        <v>2997051</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1342408</v>
+        <v>1437834</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>6552380</v>
+        <v>7363536</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>3838070</v>
+        <v>3092748</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1629441</v>
+        <v>266406</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1856981</v>
+        <v>9853779</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>6721449</v>
+        <v>3782528</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>5033894</v>
+        <v>453126</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>4305560</v>
+        <v>5742038</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>2799325</v>
+        <v>7752490</v>
       </c>
     </row>
     <row r="11">
@@ -1954,52 +1954,52 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>8476643</v>
+        <v>7813690</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>3850864</v>
+        <v>5799154</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6574735</v>
+        <v>9451239</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>5265246</v>
+        <v>2058168</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>9985295</v>
+        <v>1785322</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>895274</v>
+        <v>5789403</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>1344734</v>
+        <v>6244574</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>6060721</v>
+        <v>5368731</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1918061</v>
+        <v>4672636</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>8027694</v>
+        <v>1766963</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>9515797</v>
+        <v>6716478</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>2676276</v>
+        <v>5545946</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>8513686</v>
+        <v>7227309</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>4218907</v>
+        <v>2248658</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>6626652</v>
+        <v>9253579</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>9297393</v>
+        <v>9824399</v>
       </c>
     </row>
     <row r="12">
@@ -2009,52 +2009,52 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>8638567</v>
+        <v>9124953</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>8192890</v>
+        <v>586547</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>9135629</v>
+        <v>5893751</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>4703193</v>
+        <v>8743296</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>3160155</v>
+        <v>8412232</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1791837</v>
+        <v>329205</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>1865092</v>
+        <v>2545673</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1446999</v>
+        <v>2136570</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>4700115</v>
+        <v>4477760</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>4280157</v>
+        <v>3002958</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>367268</v>
+        <v>9277965</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>2800679</v>
+        <v>620349</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>5936521</v>
+        <v>2860403</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>9825055</v>
+        <v>7453269</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2533556</v>
+        <v>9592958</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>7827414</v>
+        <v>5745003</v>
       </c>
     </row>
     <row r="13">
@@ -2064,52 +2064,52 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>6058548</v>
+        <v>2672592</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>745167</v>
+        <v>9320219</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>617632</v>
+        <v>5592147</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7382691</v>
+        <v>4611647</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1617282</v>
+        <v>7980227</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>398333</v>
+        <v>5279922</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>3458076</v>
+        <v>9618452</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>6067412</v>
+        <v>9139314</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>8380492</v>
+        <v>3099581</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>284119</v>
+        <v>9101320</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>6993811</v>
+        <v>2315193</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>5714973</v>
+        <v>4329696</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>1317776</v>
+        <v>6616797</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>3739946</v>
+        <v>336083</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>797533</v>
+        <v>7520168</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>6389303</v>
+        <v>9648476</v>
       </c>
     </row>
     <row r="14">
@@ -2119,52 +2119,52 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>4989094</v>
+        <v>1128914</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>4272418</v>
+        <v>853994</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>268782</v>
+        <v>7554568</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>294568</v>
+        <v>6268410</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6510677</v>
+        <v>7218020</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1849638</v>
+        <v>5300549</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>7305861</v>
+        <v>5194762</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>9745687</v>
+        <v>5962337</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>122022</v>
+        <v>2755114</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>71002</v>
+        <v>7148530</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>1710210</v>
+        <v>4852461</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>3908936</v>
+        <v>6742048</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>6564997</v>
+        <v>2753212</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>1878753</v>
+        <v>3017557</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>959051</v>
+        <v>6032335</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>2959363</v>
+        <v>6528333</v>
       </c>
     </row>
     <row r="15">
@@ -2174,52 +2174,52 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2120379</v>
+        <v>1678958</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2213144</v>
+        <v>4190722</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5670271</v>
+        <v>3863933</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>6605698</v>
+        <v>2473478</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>7485902</v>
+        <v>6180842</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>7941032</v>
+        <v>8450291</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>164080</v>
+        <v>36157</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>183639</v>
+        <v>1320126</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>6120892</v>
+        <v>292871</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>628467</v>
+        <v>707565</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>6740548</v>
+        <v>6464845</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>6391547</v>
+        <v>7727777</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>6599103</v>
+        <v>4389382</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>4576187</v>
+        <v>2734987</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>8086583</v>
+        <v>1517475</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>4833515</v>
+        <v>937548</v>
       </c>
     </row>
     <row r="16">
@@ -2229,52 +2229,52 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>5803758</v>
+        <v>6123884</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1774327</v>
+        <v>9639674</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2054661</v>
+        <v>7725403</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5780282</v>
+        <v>9486563</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>8140814</v>
+        <v>8259127</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>4844291</v>
+        <v>4905272</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>8634642</v>
+        <v>9642501</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>4447354</v>
+        <v>2061773</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>7390030</v>
+        <v>7001435</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>8932507</v>
+        <v>1301247</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>9124291</v>
+        <v>4943467</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>4498492</v>
+        <v>8031132</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>7028290</v>
+        <v>5895204</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>8237353</v>
+        <v>709586</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>3297504</v>
+        <v>9918662</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>6973935</v>
+        <v>7485571</v>
       </c>
     </row>
     <row r="17">
@@ -2284,52 +2284,52 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>9396126</v>
+        <v>3355539</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>7604427</v>
+        <v>5695712</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>9450333</v>
+        <v>2576473</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5771267</v>
+        <v>9458598</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1864484</v>
+        <v>4166095</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>468846</v>
+        <v>1958763</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>9750646</v>
+        <v>9830992</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>8544294</v>
+        <v>5799331</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>6376055</v>
+        <v>837778</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>7425801</v>
+        <v>5486785</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>3374796</v>
+        <v>2142882</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>30597</v>
+        <v>4689516</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>9922048</v>
+        <v>6285784</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>604404</v>
+        <v>6070117</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>2997599</v>
+        <v>1800932</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>2836678</v>
+        <v>5464805</v>
       </c>
     </row>
     <row r="18">
@@ -2339,52 +2339,52 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>4074375</v>
+        <v>3049617</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>9788766</v>
+        <v>8653018</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>3193630</v>
+        <v>3589949</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7559889</v>
+        <v>9802491</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>7795867</v>
+        <v>361702</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>5225729</v>
+        <v>65291</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>7199595</v>
+        <v>3460156</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>7804493</v>
+        <v>2251317</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>5195932</v>
+        <v>4995940</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>179329</v>
+        <v>4453115</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>6063037</v>
+        <v>3852249</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>6088547</v>
+        <v>3451449</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>8312006</v>
+        <v>7816607</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>9220432</v>
+        <v>8909467</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>8989707</v>
+        <v>2341300</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>9923462</v>
+        <v>6918507</v>
       </c>
     </row>
     <row r="19">
@@ -2394,52 +2394,52 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>7611827</v>
+        <v>1850364</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1378185</v>
+        <v>4187052</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1725739</v>
+        <v>4559129</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>8499186</v>
+        <v>5241226</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1492377</v>
+        <v>9683421</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>3558075</v>
+        <v>5300907</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>4500421</v>
+        <v>6887509</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>3000741</v>
+        <v>8722585</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>5618974</v>
+        <v>9990447</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>5459010</v>
+        <v>6744390</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>5767563</v>
+        <v>5333478</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>2496736</v>
+        <v>4750114</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>8338076</v>
+        <v>698431</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>6574460</v>
+        <v>4715565</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>5306011</v>
+        <v>7704938</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>1795256</v>
+        <v>9910066</v>
       </c>
     </row>
   </sheetData>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-04-25 11:29:47</t>
+          <t>2026-04-26 20:37:16</t>
         </is>
       </c>
     </row>
